--- a/output/sliding_window_results_window_11.xlsx
+++ b/output/sliding_window_results_window_11.xlsx
@@ -460,16 +460,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>36.3</v>
+        <v>56.1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.69391315212771</v>
+        <v>64.14459897680865</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.6060868478722909</v>
+        <v>8.044598976808651</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3673412671637695</v>
+        <v>64.71557269767079</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>38.5</v>
+        <v>60</v>
       </c>
       <c r="C3" t="n">
-        <v>38.09614589982041</v>
+        <v>64.32267993037935</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4038541001795934</v>
+        <v>4.322679930379351</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1630981342318691</v>
+        <v>18.68556178050443</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>40.1</v>
+        <v>63.9</v>
       </c>
       <c r="C4" t="n">
-        <v>39.42365405124451</v>
+        <v>73.02040018727415</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6763459487554897</v>
+        <v>9.12040018727415</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4574438423979635</v>
+        <v>83.18169957603035</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>41.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>40.74452914296792</v>
+        <v>77.9166169312864</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7554708570320798</v>
+        <v>7.316616931286404</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5707362158247852</v>
+        <v>53.53288331918688</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>43.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>43.96188567141104</v>
+        <v>84.61706370287877</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2618856714110365</v>
+        <v>3.717063702878761</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06858410489040936</v>
+        <v>13.81656257125877</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>48.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>46.39812149496419</v>
+        <v>92.1800503138839</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.701878505035815</v>
+        <v>3.080050313883902</v>
       </c>
       <c r="E7" t="n">
-        <v>2.89639044590294</v>
+        <v>9.486709936056323</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>51.35514247900846</v>
+        <v>88.08479805879563</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.644857520991536</v>
+        <v>-6.915201941204373</v>
       </c>
       <c r="E8" t="n">
-        <v>2.705556264362422</v>
+        <v>47.82001788763672</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>56.1</v>
+        <v>98.8</v>
       </c>
       <c r="C9" t="n">
-        <v>55.1763857042624</v>
+        <v>101.8796908148016</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9236142957376003</v>
+        <v>3.079690814801566</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8530633672908635</v>
+        <v>9.484495514773133</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>103.3</v>
       </c>
       <c r="C10" t="n">
-        <v>58.74041727474626</v>
+        <v>101.4718291249694</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.259582725253736</v>
+        <v>-1.82817087503058</v>
       </c>
       <c r="E10" t="n">
-        <v>1.586548641757629</v>
+        <v>3.342208748310075</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>63.9</v>
+        <v>107</v>
       </c>
       <c r="C11" t="n">
-        <v>62.28141750134478</v>
+        <v>110.953721510737</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.618582498655222</v>
+        <v>3.953721510737012</v>
       </c>
       <c r="E11" t="n">
-        <v>2.619809304952982</v>
+        <v>15.63191378446456</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>70.59999999999999</v>
+        <v>108.7</v>
       </c>
       <c r="C12" t="n">
-        <v>69.87812782415247</v>
+        <v>120.0821455118284</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7218721758475226</v>
+        <v>11.3821455118284</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5210994382628366</v>
+        <v>129.5532364524353</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>80.90000000000001</v>
+        <v>112.7</v>
       </c>
       <c r="C13" t="n">
-        <v>78.48100131603444</v>
+        <v>121.4020925715519</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.418998683965569</v>
+        <v>8.702092571551859</v>
       </c>
       <c r="E13" t="n">
-        <v>5.851554633027154</v>
+        <v>75.72641512385805</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>89.09999999999999</v>
+        <v>117.2</v>
       </c>
       <c r="C14" t="n">
-        <v>86.64066059411078</v>
+        <v>129.2743499438502</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.45933940588921</v>
+        <v>12.07434994385015</v>
       </c>
       <c r="E14" t="n">
-        <v>6.048350313359493</v>
+        <v>145.7899265665542</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="n">
-        <v>95</v>
+        <v>123.1</v>
       </c>
       <c r="C15" t="n">
-        <v>92.48068401545603</v>
+        <v>129.0901249828472</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.519315984543965</v>
+        <v>5.990124982847192</v>
       </c>
       <c r="E15" t="n">
-        <v>6.346953029978729</v>
+        <v>35.88159731013007</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="n">
-        <v>98.8</v>
+        <v>128.9</v>
       </c>
       <c r="C16" t="n">
-        <v>96.39271788474576</v>
+        <v>131.8465164958994</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.407282115254233</v>
+        <v>2.946516495899346</v>
       </c>
       <c r="E16" t="n">
-        <v>5.795007182422895</v>
+        <v>8.681959460606958</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>103.3</v>
+        <v>135.1</v>
       </c>
       <c r="C17" t="n">
-        <v>100.8137101006588</v>
+        <v>139.1631406839315</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.486289899341187</v>
+        <v>4.06314068393155</v>
       </c>
       <c r="E17" t="n">
-        <v>6.181637463566013</v>
+        <v>16.50911221741974</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>107</v>
+        <v>139.4</v>
       </c>
       <c r="C18" t="n">
-        <v>105.0779945149398</v>
+        <v>143.5166555085397</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.922005485060225</v>
+        <v>4.116655508539651</v>
       </c>
       <c r="E18" t="n">
-        <v>3.694105084601592</v>
+        <v>16.94685257598985</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>108.7</v>
+        <v>143.8</v>
       </c>
       <c r="C19" t="n">
-        <v>107.0790593030598</v>
+        <v>150.7728044185194</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.620940696940252</v>
+        <v>6.972804418519388</v>
       </c>
       <c r="E19" t="n">
-        <v>2.627448742997151</v>
+        <v>48.6200014589235</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>112.7</v>
+        <v>147.2</v>
       </c>
       <c r="C20" t="n">
-        <v>111.9309439951657</v>
+        <v>156.1696880065602</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7690560048343116</v>
+        <v>8.969688006560176</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5914471385717127</v>
+        <v>80.45530293502947</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>117.2</v>
+        <v>151.8</v>
       </c>
       <c r="C21" t="n">
-        <v>114.9186503603067</v>
+        <v>160.106409255012</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.281349639693261</v>
+        <v>8.306409255011999</v>
       </c>
       <c r="E21" t="n">
-        <v>5.20455617852857</v>
+        <v>68.996434711749</v>
       </c>
     </row>
     <row r="22">
@@ -803,11 +803,11 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-28.93483771947206</v>
+        <v>107.4153769303546</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>55.15073079409177</v>
+        <v>946.8584646285882</v>
       </c>
     </row>
     <row r="23">
@@ -820,7 +820,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>2.757536539704589</v>
+        <v>47.34292323142941</v>
       </c>
     </row>
   </sheetData>
